--- a/data/trans_orig/KIDM_A_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/KIDM_A_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2007 (tasa de respuesta: 87,69%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2007 (tasa de respuesta: 87,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>5450</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7813</t>
+          <t>7332</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2228</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9301</t>
+          <t>10257</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,47%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103972</t>
+          <t>103269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>113137</t>
+          <t>113618</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>119637</t>
+          <t>119603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>220367</t>
+          <t>219411</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>227554</t>
+          <t>227440</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9175</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>658</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3328</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12166</t>
+          <t>11623</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165290</t>
+          <t>165109</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172505</t>
+          <t>172458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175610</t>
+          <t>175118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180557</t>
+          <t>180554</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>343511</t>
+          <t>344054</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>352260</t>
+          <t>352349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>11054</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2687</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>11529</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>6774</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>17910</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>271214</t>
+          <t>272130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>280389</t>
+          <t>280393</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>291820</t>
+          <t>290633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299475</t>
+          <t>299655</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>566540</t>
+          <t>567436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>578173</t>
+          <t>578572</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2012 (tasa de respuesta: 90,72%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2012 (tasa de respuesta: 90,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>790</t>
+          <t>792</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3412</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2042,12 +2042,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>5816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17040</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132235</t>
+          <t>132092</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138573</t>
+          <t>138571</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135810</t>
+          <t>135937</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144793</t>
+          <t>144694</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>270528</t>
+          <t>271279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>281589</t>
+          <t>281752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2882</t>
+          <t>3382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11611</t>
+          <t>11294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9395</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6526</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16713</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141235</t>
+          <t>141552</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>149964</t>
+          <t>149464</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>155076</t>
+          <t>154612</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>162083</t>
+          <t>162141</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300139</t>
+          <t>299793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310897</t>
+          <t>310326</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>7120</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17923</t>
+          <t>17336</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13781</t>
+          <t>13409</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28689</t>
+          <t>28347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>276813</t>
+          <t>275706</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>287302</t>
+          <t>286730</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>294289</t>
+          <t>294876</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>305476</t>
+          <t>305092</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575732</t>
+          <t>576074</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>590640</t>
+          <t>591012</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -3056,7 +3056,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2016 (tasa de respuesta: 89,47%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2016 (tasa de respuesta: 89,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1394</t>
+          <t>1378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8767</t>
+          <t>8268</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>3211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11708</t>
+          <t>12249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3336,12 +3336,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165859</t>
+          <t>166111</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>171577</t>
+          <t>171584</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>155131</t>
+          <t>155630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>162504</t>
+          <t>162520</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>324425</t>
+          <t>323884</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>333411</t>
+          <t>332922</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6217</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>5986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1621</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>8763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3679,12 +3679,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145716</t>
+          <t>145928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>151322</t>
+          <t>151179</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>156230</t>
+          <t>156121</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304533</t>
+          <t>305277</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>312314</t>
+          <t>312419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -3937,12 +3937,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2254</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9348</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2453</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>11252</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6434</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16695</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4022,12 +4022,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314820</t>
+          <t>314949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>321914</t>
+          <t>322012</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314284</t>
+          <t>314754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323553</t>
+          <t>323568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>633479</t>
+          <t>633860</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643740</t>
+          <t>644278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -4315,7 +4315,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si su salud general autopercibida es regular o mala (autopercepción menor) en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>619</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4525,82 +4525,82 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1623</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5026</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>5,06%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>3857</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1491</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>8908</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,66%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1623</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5680</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,72%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>3857</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1476</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>8856</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>62633</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>68138</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4638,82 +4638,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>97742</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>94339</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>99365</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>98,37%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>94,94%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>164265</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>159214</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>166631</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>94,7%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97742</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>93685</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,37%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,28%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>164265</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>159266</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>166646</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2066</t>
+          <t>2277</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>164</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6284</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140481</t>
+          <t>140270</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167734</t>
+          <t>167097</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>173481</t>
+          <t>173487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5016,12 +5016,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309824</t>
+          <t>309914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>315782</t>
+          <t>315482</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>684</t>
+          <t>743</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6553</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8430</t>
+          <t>9551</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2712</t>
+          <t>2673</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -5309,12 +5309,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>204751</t>
+          <t>204124</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>210620</t>
+          <t>210561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>264586</t>
+          <t>263465</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>272001</t>
+          <t>271983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>472475</t>
+          <t>471831</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>481608</t>
+          <t>481647</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
     </row>
